--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google Data Engineer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>City of Rockville</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, ETL, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063d41992d4b3402</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffba52098259ac2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1c45f198f8f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>City of Rockville</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, ETL, ELT, Power BI, MLOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,75 +566,40 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffba52098259ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Sr Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Major League Baseball (MLB)</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae4dfa2efb93cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9b55caa3b9d44424</t>
         </is>

--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,140 +468,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>City of Rockville</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, ETL, ELT, Power BI, MLOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffba52098259ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Solution Architect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Customer Reliability Engineer, Airflow</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Philadelphia, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>11.1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b55caa3b9d44424</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>bet365</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=408ab6603d114356</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>AWS SysOp Admin/DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,84 +601,84 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Software Engineer - 2373611</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,147 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Customer Reliability Engineer, Airflow</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Philadelphia, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>bet365</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Denver, CO, US USA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>10.4</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=408ab6603d114356</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VINMAR INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Salesforce Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - 2373611</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,137 +671,137 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Software Engineer - Austin, TX - 2373630</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bet365</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,40 +811,670 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=408ab6603d114356</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Senior Data Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Downers Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The University of Michigan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Architect - C2H - Onsite</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Flower Mound, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer - 2373611</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Solution Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Customer Reliability Engineer, Airflow</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Philadelphia, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Trulieve</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>OneMain Financial</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data and AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JELLYFISH</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>bet365</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=408ab6603d114356</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>AI Systems Engineer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>VINMAR INTERNATIONAL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D30" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
         </is>

--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS SysOp Admin/DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Green Mountain Power</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Colchester, VT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=3d9f58a4baa94d06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS SysOp Admin/DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,77 +556,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Salesforce Architect</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Salesforce Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+          <t>Software Engineer: Full-Stack Web Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Nanobiosym</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Scala Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer - Austin, TX - 2373630</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=d57566bba0a6ced1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - 2373611</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Software Engineer - 2373611</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>bet365</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Vertex AI, Spark, Snowflake, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,42 +1441,392 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=408ab6603d114356</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e753d624ac7894</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Customer Reliability Engineer, Airflow</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Philadelphia, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Trulieve</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tenable</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OneMain Financial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DAS Federal</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Gaithersburg, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data and AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JELLYFISH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ZENO Group</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>AI Systems Engineer</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>VINMAR INTERNATIONAL</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D39" t="n">
         <v>10.4</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - 2373638</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS SysOp Admin/DevOps Engineer</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>24.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Lambda, Kinesis, S3, SQS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4c425e913ad44b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS SysOp Admin/DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
+          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
+          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Salesforce Architect</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
+          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer: Full-Stack Web Developer</t>
+          <t>Salesforce Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nanobiosym</t>
+          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
+          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>Software Engineer: Full-Stack Web Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nanobiosym</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Scala Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+          <t>Senior Scala Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Austin, TX - 2373630</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57566bba0a6ced1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - 2373611</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - 2373611</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Spark, Snowflake, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e753d624ac7894</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+          <t>AWS, RDS, Azure, Vertex AI, Spark, Snowflake, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e753d624ac7894</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>DAS Federal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VINMAR INTERNATIONAL</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373638</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VINMAR INTERNATIONAL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,15 +1816,50 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - 2373638</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
         </is>

--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=0d49a70c4f87ce0f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
+          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
+          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Salesforce Architect</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
+          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer: Full-Stack Web Developer</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nanobiosym</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
+          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Avaya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>Salesforce Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Software Engineer: Full-Stack Web Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Nanobiosym</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Scala Engineer</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
+          <t>https://www.indeed.com/viewjob?jk=56a11b4a8e808497</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Specialist - Software Development &amp; Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Scala Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer - Austin, TX - 2373630</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - 2373611</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3bab45b84b040d</t>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Spark, Snowflake, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e753d624ac7894</t>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Software Engineer - 2373611</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>New Boston, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VINMAR INTERNATIONAL</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,40 +1826,670 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Solutions Architect II - Omnichannel</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Five Below</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JCTM</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tenable</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OneMain Financial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Database Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DAS Federal</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Gaithersburg, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Compass Group USA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56503a1394bbff7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Coverys</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Associate Actuary</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Wildfire Defense Systems</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bozeman, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Associate Actuary</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Wildfire Defense Systems</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data and AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JELLYFISH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Intern - Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rad Cube LLC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data &amp; Integrations Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Alternate Solutions Health Network</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ZENO Group</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Kafka Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>VINMAR INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Senior Software Engineer - 2373638</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D59" t="n">
         <v>10.4</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
         </is>

--- a/results/job_matches_2026-06-29.xlsx
+++ b/results/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,165 +573,165 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d49a70c4f87ce0f</t>
+          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=b91053d73a5b33fa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps</t>
+          <t>Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
+          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
+          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
+          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Salesforce Architect</t>
+          <t>Software Engineer III - ATI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer: Full-Stack Web Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nanobiosym</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=b5b0482fe6c4872a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Administrator</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a11b4a8e808497</t>
+          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0732c17d73a147f5</t>
+          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Specialist - Software Development &amp; Engineering</t>
+          <t>AWS Software Engineer III-ETL/AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Scala Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Avaya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
+          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4607a264c3f31959</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>John L. Lowery &amp; Associates, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=7e20ae31f3885724</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Salesforce Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>RAPSYS TECHNOLOGIES PTE. LTD.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=6a013e1c627f048a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Specialist - Software Development &amp; Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=56a11b4a8e808497</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfee67e7ec30f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - 2373611</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Scala Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Senior Software Engineer - Austin, TX - 2373630</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Boston, IL, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
+          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solutions Architect II - Omnichannel</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0440c7931c20ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Database Engineer (contract)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Engineer - 2373611</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56503a1394bbff7d</t>
+          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Coverys</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Associate Dir, Full Stack Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Intern - Full Stack Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rad Cube LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1996dbb61f895d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+          <t>https://www.indeed.com/viewjob?jk=175e9f8a6f832243</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior NoSQL Technical Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Timestream, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd6b83169c92194</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>INFORMATION SYSTEMS OFFICER, P3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab00abb249e3052</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VINMAR INTERNATIONAL</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New Boston, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, RDS, PostgreSQL, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,42 +2456,1092 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Customer Reliability Engineer, Airflow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Philadelphia, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SCAN Health Plan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Long Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Trulieve</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>IT Analyst III - Database Administrator</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>State of Utah</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>West Jordan, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, BigQuery, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=178228f9966dd35c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Solutions Architect II - Omnichannel</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Five Below</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JCTM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tenable</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Database Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DAS Federal</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Gaithersburg, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sr. Full Stack Software Engineer, Jersey City, NJ - Onsite | In-person presence is mandatory</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Next Gen Software Solutions</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b357357f3cb8f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Search Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Vizient, Inc.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Edina, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vizient, Inc.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Edina, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Compass Group USA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56503a1394bbff7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Coverys</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Asure Software</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6785b7100612a9df</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Associate Actuary</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Wildfire Defense Systems</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bozeman, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Associate Actuary</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Wildfire Defense Systems</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Data and AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JELLYFISH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Intern - Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Rad Cube LLC</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data &amp; Integrations Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Alternate Solutions Health Network</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ZENO Group</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Internally Deployed Products</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ClickUp</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, GCP, BigQuery, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sr Automation Engineer Sales</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Raya Workforce</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Woodstock, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Software Engineer - Java and Spring WebFlux</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd37326d3fa0289f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - US</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GreenBox Capital</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Agentic AI Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da0e10d1b2e6cc95</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Kafka Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>Senior Software Engineer - 2373638</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D88" t="n">
         <v>10.4</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
         </is>
       </c>
     </row>
